--- a/Afrimart-KollyBright-Sales-Dataset.xlsx
+++ b/Afrimart-KollyBright-Sales-Dataset.xlsx
@@ -8,28 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\01_project_builders_DA-main\01_project_builders_DA-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{48D68795-09C9-48EA-B676-39C245FC93F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2A6E804-A06E-4471-8BE2-04561FF72927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
-    <sheet name="New Data" sheetId="2" r:id="rId2"/>
-    <sheet name="Notes" sheetId="3" r:id="rId3"/>
-    <sheet name="Pivot Table" sheetId="4" r:id="rId4"/>
-    <sheet name="Dashboard" sheetId="5" r:id="rId5"/>
+    <sheet name="Cleaned Data" sheetId="2" r:id="rId2"/>
+    <sheet name="Pivot Table" sheetId="4" r:id="rId3"/>
+    <sheet name="Dashboard" sheetId="5" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="Slicer_Country">#N/A</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId6"/>
+    <pivotCache cacheId="1" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
       <x14:slicerCaches>
-        <x14:slicerCache r:id="rId7"/>
+        <x14:slicerCache r:id="rId6"/>
       </x14:slicerCaches>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
@@ -301,7 +300,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[AfriMart_Sales_Dataset().xlsx]Pivot Table!PivotTable1</c:name>
+    <c:name>[Afrimart-KollyBright-Sales-Dataset.xlsx]Pivot Table!PivotTable1</c:name>
     <c:fmtId val="8"/>
   </c:pivotSource>
   <c:chart>
@@ -1071,7 +1070,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[AfriMart_Sales_Dataset().xlsx]Pivot Table!PivotTable6</c:name>
+    <c:name>[Afrimart-KollyBright-Sales-Dataset.xlsx]Pivot Table!PivotTable6</c:name>
     <c:fmtId val="3"/>
   </c:pivotSource>
   <c:chart>
@@ -1832,7 +1831,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[AfriMart_Sales_Dataset().xlsx]Pivot Table!PivotTable7</c:name>
+    <c:name>[Afrimart-KollyBright-Sales-Dataset.xlsx]Pivot Table!PivotTable7</c:name>
     <c:fmtId val="4"/>
   </c:pivotSource>
   <c:chart>
@@ -2505,7 +2504,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[AfriMart_Sales_Dataset().xlsx]Pivot Table!PivotTable9</c:name>
+    <c:name>[Afrimart-KollyBright-Sales-Dataset.xlsx]Pivot Table!PivotTable9</c:name>
     <c:fmtId val="4"/>
   </c:pivotSource>
   <c:chart>
@@ -5260,86 +5259,6 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>590550</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="Rectangle 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{212955AE-78AE-D6DF-4D44-A8DEAFA5DEC5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2838450" y="609600"/>
-          <a:ext cx="3238500" cy="1581150"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>7  columns,</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0"/>
-            <a:t> 700 rows </a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="en-US" sz="1100" baseline="0"/>
-          </a:br>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0"/>
-            <a:t>3 dimensions, 4 metric</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -11826,7 +11745,119 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DA90052B-DDCD-42A2-8D17-8FB12E215151}" name="PivotTable19" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{39038E34-FD31-49A6-8F8D-B7D6B7ADF5C5}" name="PivotTable6" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+  <location ref="D7:F18" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="11">
+        <item x="7"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="9"/>
+        <item x="4"/>
+        <item x="8"/>
+        <item x="6"/>
+        <item x="5"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="11">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name="Sum of Profit" fld="5" baseField="0" baseItem="0"/>
+    <dataField name="Sum of Revenue" fld="3" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="2">
+    <chartFormat chart="3" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DA90052B-DDCD-42A2-8D17-8FB12E215151}" name="PivotTable19" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C2:C3" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="8">
     <pivotField showAll="0">
@@ -11873,8 +11904,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{276BB5F4-F68D-4A0D-90BE-3882931C53DF}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="21">
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{276BB5F4-F68D-4A0D-90BE-3882931C53DF}" name="PivotTable7" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="21">
   <location ref="A21:C29" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField showAll="0">
@@ -11987,8 +12018,104 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1C1A34C8-5047-4443-A666-8DF974B95D3C}" name="PivotTable18" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{64482FD3-3546-4C05-96A0-96A8BACDFEFF}" name="PivotTable9" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+  <location ref="G7:H15" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField showAll="0">
+      <items count="11">
+        <item x="7"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="9"/>
+        <item x="4"/>
+        <item x="8"/>
+        <item x="6"/>
+        <item x="5"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="8">
+        <item x="4"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="8">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Units Sold" fld="2" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="4" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1C1A34C8-5047-4443-A666-8DF974B95D3C}" name="PivotTable18" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="B2:B3" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="8">
     <pivotField showAll="0">
@@ -12035,8 +12162,104 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D5BD705F-B633-4420-A159-52D65349E69E}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="23">
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{160BE447-6214-44B6-BC6F-CEECA9935041}" name="PivotTable12" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A2:A3" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="8">
+    <pivotField showAll="0">
+      <items count="11">
+        <item x="7"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="9"/>
+        <item x="4"/>
+        <item x="8"/>
+        <item x="6"/>
+        <item x="5"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField dataField="1" numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Profit" fld="5" baseField="0" baseItem="0" numFmtId="164"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DF754048-1FD9-4CA3-B99E-B9704F1B2477}" name="PivotTable21" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="E2:E3" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="8">
+    <pivotField showAll="0">
+      <items count="11">
+        <item x="7"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="9"/>
+        <item x="4"/>
+        <item x="8"/>
+        <item x="6"/>
+        <item x="5"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField dataField="1" numFmtId="44" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Cost" fld="4" baseField="0" baseItem="0" numFmtId="44"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D5BD705F-B633-4420-A159-52D65349E69E}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="23">
   <location ref="A7:C18" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField axis="axisRow" showAll="0">
@@ -12147,8 +12370,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6661BA65-F035-427E-AD79-340433BDA808}" name="PivotTable20" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6661BA65-F035-427E-AD79-340433BDA808}" name="PivotTable20" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="D2:D3" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="8">
     <pivotField showAll="0">
@@ -12182,310 +12405,6 @@
   </colItems>
   <dataFields count="1">
     <dataField name="Sum of Units Sold" fld="2" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{39038E34-FD31-49A6-8F8D-B7D6B7ADF5C5}" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
-  <location ref="D7:F18" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="8">
-    <pivotField axis="axisRow" showAll="0">
-      <items count="11">
-        <item x="7"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="9"/>
-        <item x="4"/>
-        <item x="8"/>
-        <item x="6"/>
-        <item x="5"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="11">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-  </colItems>
-  <dataFields count="2">
-    <dataField name="Sum of Profit" fld="5" baseField="0" baseItem="0"/>
-    <dataField name="Sum of Revenue" fld="3" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="2">
-    <chartFormat chart="3" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="3" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{64482FD3-3546-4C05-96A0-96A8BACDFEFF}" name="PivotTable9" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
-  <location ref="G7:H15" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="8">
-    <pivotField showAll="0">
-      <items count="11">
-        <item x="7"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="9"/>
-        <item x="4"/>
-        <item x="8"/>
-        <item x="6"/>
-        <item x="5"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="8">
-        <item x="4"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="6"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="8">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Units Sold" fld="2" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="4" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{160BE447-6214-44B6-BC6F-CEECA9935041}" name="PivotTable12" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A2:A3" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="8">
-    <pivotField showAll="0">
-      <items count="11">
-        <item x="7"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="9"/>
-        <item x="4"/>
-        <item x="8"/>
-        <item x="6"/>
-        <item x="5"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="44" showAll="0"/>
-    <pivotField numFmtId="44" showAll="0"/>
-    <pivotField dataField="1" numFmtId="164" showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Profit" fld="5" baseField="0" baseItem="0" numFmtId="164"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DF754048-1FD9-4CA3-B99E-B9704F1B2477}" name="PivotTable21" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="E2:E3" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="8">
-    <pivotField showAll="0">
-      <items count="11">
-        <item x="7"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="9"/>
-        <item x="4"/>
-        <item x="8"/>
-        <item x="6"/>
-        <item x="5"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="44" showAll="0"/>
-    <pivotField dataField="1" numFmtId="44" showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Cost" fld="4" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -43216,19 +43135,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{814D9AC6-7009-44FB-A5B4-6B228C3F85CA}">
-  <sheetPr>
-    <tabColor theme="9" tint="-0.249977111117893"/>
-  </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C97CC2C-5140-422F-9476-754E3BBC8C0B}">
   <dimension ref="A1:H29"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -43721,7 +43627,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D884235C-FC1E-47CC-97C6-631D3CC0A2CE}">
   <dimension ref="A1:M46"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
